--- a/daily_matches/job_matches_2026-03-05.xlsx
+++ b/daily_matches/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>Associate GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, Azure ML, MLflow</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
+          <t>https://www.indeed.com/viewjob?jk=a026b7b596edb95a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Associate GenAI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a132dfc777bcff0a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Associate GenAI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521c8eaf0e3efb60</t>
+          <t>https://www.indeed.com/viewjob?jk=6708bcec429a4f9d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Playwright Automation Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035276d2ab91c33a</t>
+          <t>https://www.indeed.com/viewjob?jk=7135bbd091f6e927</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Software Engineer - Hybrid Charlotte, NC US</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f46c3f43f76013</t>
+          <t>https://www.indeed.com/viewjob?jk=96fa7712617c2b0f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Software Engineer - Hybrid Charlotte, NC US</t>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf1e5a5c5e15842</t>
+          <t>https://www.indeed.com/viewjob?jk=dea3b0f5ba959d7e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Gen AI Application</t>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,1582 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276f2679fa9e6c41</t>
+          <t>https://www.indeed.com/viewjob?jk=d6acb25c99f27c0d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=621709c162140604</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8a6366c30e8284</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1e3299bb98da7e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62c3c540d75e6a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1186a0648008358</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8eb5bfe6a3f00c18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65db1fbf0b744c4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6390e3b8ede6beb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07a6d419a08174a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caab9641a78e78cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c56690205eacf1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74b107f1bfd991f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eba887cd0ca9245</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80994247ad6663e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cf1ff53fba4dc32</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acd016d84ab35df8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=994bbac81cd17f77</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5367f6a728a9f33</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30a5af9146bcf729</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63142d8ecc3d4d86</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21034ca2a9df4ed0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46305193c28f6e90</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=485e7e23c30e6fcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99d07b49921502d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32a1abce70103b03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=062782b468665ab3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3efa0710def94d00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a5f885c321034d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91932fdabc16594f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a8b68ad8aae6dda</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Developer III</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RealPage Inc</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b35fdbabb8c95c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer - Authentication</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pindrop</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IT Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Novolex</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lake Forest, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Dataflow, Databricks, PySpark, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Scientist - National Federal Tax Services</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6924bfb8fd4f7afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Scientist - National Federal Tax Services</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b8c1eb33e6b1ba3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Scientist (Remote)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=345031cc2dcdfebc</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=297b782722b3fa99</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Container Platform Engineer*** Hybrid in Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1da41e74ec65cda</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Container Platform Engineer*** Hybrid in Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LexisNexis Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5add27442fbeffb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Senior Scientist</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>City National Bank</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669cf2add69e840e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Senior Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>City National Bank</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2b27e9797faa9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Gen AI Application</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5e6953071e03c7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Senior Data Scientist, Gen AI Foundation</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Genentech</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D53" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Data Scientist, Generative AI, LangChain, RAG, Git, SQL, R, Scala, Optimization</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9968f242aa233</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f212829af1f3caa</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-05.xlsx
+++ b/daily_matches/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,82 +468,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate GenAI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, S3, Glue, Athena, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a026b7b596edb95a</t>
+          <t>https://www.indeed.com/viewjob?jk=64783609821b5058</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate GenAI Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a132dfc777bcff0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate GenAI Engineer</t>
+          <t>Senior Associate -Applied AI Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,116 +552,116 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6708bcec429a4f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=447ecf288ec635dc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
+          <t>Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Snowflake, Kafka, PostgreSQL, Cassandra, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7135bbd091f6e927</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Sr Software Developer - remote opportunity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Tivity Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
+          <t>RAG, S3, Glue, Docker, CI/CD, Terraform, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fa7712617c2b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a33a7d52bc385fbe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Copilot, S3, EC2, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,1082 +671,1082 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea3b0f5ba959d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=e9beca67b7d20a92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>CCB Risk Modeling - AI ML Senior Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>RAG, Prompt Engineering, TensorFlow, XGBoost, Git, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6acb25c99f27c0d</t>
+          <t>https://www.indeed.com/viewjob?jk=46d1a166f45a539b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621709c162140604</t>
+          <t>https://www.indeed.com/viewjob?jk=434eec96fb9692b2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a6366c30e8284</t>
+          <t>https://www.indeed.com/viewjob?jk=42bb477caadfc26c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1e3299bb98da7e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4753fd98a50b3fe3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c3c540d75e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4fc325f040d982e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1186a0648008358</t>
+          <t>https://www.indeed.com/viewjob?jk=fef936da522c9af1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb5bfe6a3f00c18</t>
+          <t>https://www.indeed.com/viewjob?jk=08d09f380f70a3fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65db1fbf0b744c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=22ab1b2a49fa7cce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6390e3b8ede6beb</t>
+          <t>https://www.indeed.com/viewjob?jk=82c773741b57e6b5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a6d419a08174a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1ceb9ade56a2fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caab9641a78e78cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5fab364ee83d967c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c56690205eacf1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4fabb517af1e2ad2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b107f1bfd991f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea613e39b9985b0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba887cd0ca9245</t>
+          <t>https://www.indeed.com/viewjob?jk=bf44454d58cbbfe3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80994247ad6663e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4beac83bae3fc2f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf1ff53fba4dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=efa5606ca7937a3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd016d84ab35df8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc92d65138587fbe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=994bbac81cd17f77</t>
+          <t>https://www.indeed.com/viewjob?jk=d119769f1bd69085</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5367f6a728a9f33</t>
+          <t>https://www.indeed.com/viewjob?jk=b259a15f5d14a2ee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a5af9146bcf729</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b40aef71bf1c61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63142d8ecc3d4d86</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4b28b613349842</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21034ca2a9df4ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbc21dc9407e833</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46305193c28f6e90</t>
+          <t>https://www.indeed.com/viewjob?jk=b8fdcab3f00e210d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485e7e23c30e6fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=49700fc92efe684d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99d07b49921502d7</t>
+          <t>https://www.indeed.com/viewjob?jk=87afcc5fc764fe82</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a1abce70103b03</t>
+          <t>https://www.indeed.com/viewjob?jk=46220d0f4888dc55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Forward Deployed Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062782b468665ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a79f28b2498e75</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Software Engineer, TikTok AIGC Agentic Workflow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Kubernetes, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efa0710def94d00</t>
+          <t>https://www.indeed.com/viewjob?jk=3040dd79f0846a3c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Senior Software Engineer, TikTok AIGC Agentic Workflow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Kubernetes, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5f885c321034d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1b2bcc587c3af65e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Corporate Finance – Data Science Product Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91932fdabc16594f</t>
+          <t>https://www.indeed.com/viewjob?jk=53a8bd4dbe5c9210</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH-Full-Stack Software Engineer-Innovation_Delivery_Transformation</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, S3, Docker, Kubernetes, Git, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,532 +1756,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8b68ad8aae6dda</t>
+          <t>https://www.indeed.com/viewjob?jk=db87b6eb69c0206e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Developer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Data Lake, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35fdbabb8c95c41</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Software Engineer - Authentication</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Pindrop</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>IT Data Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Novolex</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Lake Forest, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Dataflow, Databricks, PySpark, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Data Scientist - National Federal Tax Services</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6924bfb8fd4f7afd</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data Scientist - National Federal Tax Services</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8c1eb33e6b1ba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Data Scientist (Remote)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Inspira Financial</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=345031cc2dcdfebc</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Inspira Financial</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Inspira Financial</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=297b782722b3fa99</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Container Platform Engineer*** Hybrid in Raleigh, NC</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da41e74ec65cda</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Container Platform Engineer*** Hybrid in Raleigh, NC</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LexisNexis Legal &amp; Professional</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5add27442fbeffb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Senior Scientist</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>City National Bank</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=669cf2add69e840e</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Senior Scientist</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>City National Bank</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2b27e9797faa9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, Gen AI Application</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Genentech</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e6953071e03c7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, Gen AI Foundation</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Genentech</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Git, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f212829af1f3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-05.xlsx
+++ b/daily_matches/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI &amp; GenAI Data Scientist-Senior Associate</t>
+          <t>Data Science AI Engineer, Advisor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Keras, NLTK, CI/CD, Git, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Hadoop, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db835aa77a456de</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce47473bd581bfe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, SQL</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Git, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Engineer (NYC)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>KNIT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, SQL</t>
+          <t>RAG, Copilot, Pinecone, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, SQL</t>
+          <t>AI Engineer, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,672 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=030b7f16c93fdca8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Human Resources Data Scientist</t>
+          <t>Software Engineer - AI Development</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Contrast Security</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dcf4a5bca1f04a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Implementation Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Just Appraised</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c50c661ee11a365</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GRAY MEDIA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a8daf67ffd50591</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Application Platform Architect - 6163848</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Hadoop, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3104dfd5fb3d83</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6ba4c47f4e4c7fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Azure ML, MLflow, Kubernetes, AKS, CI/CD, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dye Capital &amp; Company</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6362c0d17213b1ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6f4432715db5d58</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Quantitative Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9472e13ac87fedee</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CIBC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>11.1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, MLflow, CI/CD, Terraform, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe4ff669409db3b</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, Git, Databricks, Tableau, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ce8d0c0cafd3f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SENIOR DATA ENGINEER</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Databricks, Kafka, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Python Engineer-3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51181ae87dafa725</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GEN AI Engineer-3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47b2c01c65a3d80b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GEN AI Engineer-3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adbbcad61a0f64eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Systems Engineer Intern - Summer 2026, Ashburn</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecb06e7a65201859</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Syngenta</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Malta, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, OpenCV, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7345766a8077f0fe</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-05.xlsx
+++ b/daily_matches/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Science AI Engineer, Advisor</t>
+          <t>Sr Gen AI Engineer - NY/NJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Hadoop, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce47473bd581bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=414153fa61216b9e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Git, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (NYC)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KNIT</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
+          <t>https://www.indeed.com/viewjob?jk=79301b64d4cecf9d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Distro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python</t>
+          <t>RAG, Prompt Engineering, S3, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=030b7f16c93fdca8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc8ec91690084156</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Development</t>
+          <t>GE Aerospace Research - Knowledge Discovery &amp; High Assurance Systems Fellow Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contrast Security</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Niskayuna, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcf4a5bca1f04a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c005310d5c4f15f1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Implementation Engineer</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Just Appraised</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, Jenkins, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c50c661ee11a365</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Sales Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, Azure ML, FastAPI, Docker, Kubernetes, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=cee576d48a4cfda5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Senior Engineer - GenAI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git</t>
+          <t>Data Scientist, LangChain, RAG, Gemini, S3, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8daf67ffd50591</t>
+          <t>https://www.indeed.com/viewjob?jk=eb49e4ca9db0e17b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Data Scientist, GTM Strategy &amp; Transformation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Hadoop, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Kubernetes, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,497 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, Git, Kafka, Cassandra, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3104dfd5fb3d83</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Interactive Voice Response - AI/ML</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ba4c47f4e4c7fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CareSource</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Azure ML, MLflow, Kubernetes, AKS, CI/CD, Terraform, Python, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dye Capital &amp; Company</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6362c0d17213b1ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f4432715db5d58</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Quantitative Analyst</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9472e13ac87fedee</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CIBC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, LLaMA, Git, Databricks, Tableau, Power BI, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce8d0c0cafd3f36</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SENIOR DATA ENGINEER</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Databricks, Kafka, Tableau, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Python Engineer-3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51181ae87dafa725</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GEN AI Engineer-3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47b2c01c65a3d80b</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>GEN AI Engineer-3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=adbbcad61a0f64eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Systems Engineer Intern - Summer 2026, Ashburn</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb06e7a65201859</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Syngenta</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Malta, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, OpenCV, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7345766a8077f0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=99b060cfcba27979</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-05.xlsx
+++ b/daily_matches/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Gen AI Engineer - NY/NJ</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414153fa61216b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a775d36183c9b6d8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied Machine Learning Engineer (All Levels)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Azure ML, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79301b64d4cecf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Distro</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL, Python</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc8ec91690084156</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GE Aerospace Research - Knowledge Discovery &amp; High Assurance Systems Fellow Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Niskayuna, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Git</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c005310d5c4f15f1</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Brunswick</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, Jenkins, Git, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, Azure ML, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=7a30908fad913e8c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Azure ML, FastAPI, Docker, Kubernetes, Git, Python, R, Scala</t>
+          <t>RAG, S3, Data Lake, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,602 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee576d48a4cfda5</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer - GenAI</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Gemini, S3, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Data Lake, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb49e4ca9db0e17b</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, GTM Strategy &amp; Transformation</t>
+          <t>AI Engineer (Federal)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Urbane Systems LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9e5cdf1cc78d834</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Startup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TALENThire</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Luck Companies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Manakin Sabot, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afac4d5dd4e25f68</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=622748f17db63af2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - INDIA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Prosper, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Python Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Docker, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6ce1ed4fb631cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AlohaABA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc374e855d47b7da</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, XGBoost, LightGBM, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ba946309a887efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>United Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40cfe02d82264a50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior ML/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>11.1</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Kubernetes, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99b060cfcba27979</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58de4df9f23a6e20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>University of Nebraska at Omaha</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, MLflow, Docker, Kubernetes, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4e5409e7b4e6553</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer – Advanced Analytics &amp; Visualization</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Urbandale, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Databricks, MongoDB, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea47477c0410e576</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DATA SCIENCE INTERN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, XGBoost, LightGBM, Power BI, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c4be5b98513b7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tamarind Bio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a743d975a1feec3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Restaurant Depot</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Whitestone, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Apache Airflow, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f8011c785039505</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, Git, MongoDB, Python, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8c5ac3d88cb3903</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-05.xlsx
+++ b/daily_matches/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
+          <t>Data Scientist, Copilot, Hugging Face, TensorFlow, PyTorch, Keras, S3, Redshift, BigQuery, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=60711b668acbd0b3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Copilot, Hugging Face, TensorFlow, PyTorch, Keras, S3, Redshift, BigQuery, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a775d36183c9b6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=db8a35e2b334dacc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer (All Levels)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Azure ML, MLflow, Docker, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
+          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=4dbc8cc11556dcc9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brunswick</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, Azure ML, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a30908fad913e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=df2b5c9cf0eec003</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=479774b5e7e037b9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c567dfecd690268</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer (Federal)</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Urbane Systems LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e5cdf1cc78d834</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1b35da51c8dc0d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TALENThire</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b80ec1dbc706e8b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luck Companies</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manakin Sabot, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afac4d5dd4e25f68</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2a18560833e507</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622748f17db63af2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab12efc7435b0e12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=12cd4a83db6ad614</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python Ai Engineer</t>
+          <t>Java Backend Developer – DevOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Docker, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6ce1ed4fb631cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bbba714a0dc0e714</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AlohaABA</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc374e855d47b7da</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, PyTorch, XGBoost, LightGBM, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba946309a887efb</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United Federal Credit Union</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, BigQuery, FastAPI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cfe02d82264a50</t>
+          <t>https://www.indeed.com/viewjob?jk=d990794ae8f0f901</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior ML/AI Engineer</t>
+          <t>Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, BigQuery, FastAPI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58de4df9f23a6e20</t>
+          <t>https://www.indeed.com/viewjob?jk=9888d25c9c775385</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>University of Nebraska at Omaha</t>
+          <t>Stanley Martin Homes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, MLflow, Docker, Kubernetes, Python, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, MLflow, CI/CD, Git, Snowflake, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e5409e7b4e6553</t>
+          <t>https://www.indeed.com/viewjob?jk=f934b2c21443f198</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer – Advanced Analytics &amp; Visualization</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Databricks, MongoDB, Tableau, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, S3, CI/CD, Snowflake, Databricks, Hadoop, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea47477c0410e576</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DATA SCIENCE INTERN</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, XGBoost, LightGBM, Power BI, Python, R, Scala, Optimization</t>
+          <t>LangChain, RAG, S3, CI/CD, Snowflake, Databricks, Hadoop, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c4be5b98513b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>DevSecOps AI Automation Intern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tamarind Bio</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Terraform, Python, R</t>
+          <t>LangChain, Copilot, Hugging Face, TensorFlow, PyTorch, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a743d975a1feec3e</t>
+          <t>https://www.indeed.com/viewjob?jk=278fbc9f8c0a4e18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Restaurant Depot</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Whitestone, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Apache Airflow, Git, Python, SQL, R, Optimization</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,1582 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f8011c785039505</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, MLflow, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Gemini, AWS SageMaker, Redshift, BigQuery, Kubernetes, Apache Airflow, Snowflake, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior LLM Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, MLflow, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Gemini, AWS SageMaker, Redshift, BigQuery, Kubernetes, Apache Airflow, Snowflake, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Typescript and AWS services</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=021dcffcbccd49c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Data Sciences</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47415b20052e8050</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Docker, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae45c6236e31ece7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TWG Global AI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Associate Emerging Technology Engineer (GenAI, AWS, Claude)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Docker, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c89d6321c55611a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Python/PySpark</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, CI/CD, Databricks, PySpark, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, athenaCollector</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Athena, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a084d22a9ca9e675</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c595f778e26600</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=678f6a09a0ac0c26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6e8b8be5cf1c082</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Pinecone, PyTorch, XGBoost, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1eaccb6b4a7bdb44</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Pinecone, PyTorch, XGBoost, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6ca118450216ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Pinecone, PyTorch, XGBoost, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f6544c6044c9adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Pinecone, PyTorch, XGBoost, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8f8fc951ea5a859</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior AI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a4ca1e41eda12d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior AI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6ec1e40aeed2a41</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield of Nebraska</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Azure ML, CI/CD, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48d337d14919342b</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, Git, Hadoop, NoSQL, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc186ef9db8199a</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Advanced Analytics</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Snowflake, Databricks, MySQL, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92f0640d212f7db6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b75a7799aefeaa46</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5317c534ee6d0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e29cd258921614</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bc9b597d6b4442d</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Athena, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a28b07831a3de1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ML Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c347ec79fdcc60</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kafka, Cassandra, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f462fe0e66542762</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sr AI Application Developer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Rite-Hite</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Data Lake, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f4893366bf23b53</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faae4af1b35260e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Junior Software/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JackRabbit Tampa</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f18701bfc057487c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>10</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, Git, MongoDB, Python, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c5ac3d88cb3903</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63f808eb6713b042</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26b025f008a77697</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist - Solutions Strategy</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=256a32239f36ca7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea421f1b17e329f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6288c34b9f40c7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cfb1029e632cf3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c15e34d0acb55e95</t>
         </is>
       </c>
     </row>
